--- a/clustering/median of 4 clusters (factoriescap_s (usage) 0 visnorm).xlsx
+++ b/clustering/median of 4 clusters (factoriescap_s (usage) 0 visnorm).xlsx
@@ -1,37 +1,75 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Albert\.spyder-py3\ITMO-3\clustering\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12885"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+  <si>
+    <t>clust</t>
+  </si>
+  <si>
+    <t>factoriescap_s</t>
+  </si>
+  <si>
+    <t>ITusage_s</t>
+  </si>
+  <si>
+    <t>AIusage_s</t>
+  </si>
+  <si>
+    <t>BDusage_s</t>
+  </si>
+  <si>
+    <t>AIusage_s % in IT</t>
+  </si>
+  <si>
+    <t>BDusage_s % in IT</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +84,54 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Процентный" xfId="1" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,110 +419,215 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="16.7109375" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="19.42578125" customWidth="1"/>
+    <col min="7" max="7" width="20.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>clust</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>factoriescap_s</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>ITusage_s</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>AIusage_s</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>BDusage_s</t>
-        </is>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
         <v>0</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="3">
         <v>239465.7845999992</v>
       </c>
-      <c r="C2" t="n">
-        <v>125.999999999999</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3.999999999999982</v>
-      </c>
-      <c r="E2" t="n">
-        <v>22.99999999999975</v>
+      <c r="C2" s="2">
+        <v>125.99999999999901</v>
+      </c>
+      <c r="D2" s="2">
+        <v>3.9999999999999818</v>
+      </c>
+      <c r="E2" s="2">
+        <v>22.999999999999751</v>
+      </c>
+      <c r="F2" s="4">
+        <f>D2/C2</f>
+        <v>3.1746031746031855E-2</v>
+      </c>
+      <c r="G2" s="4">
+        <f>E2/C2</f>
+        <v>0.182539682539682</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" t="n">
-        <v>1433541.348599997</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1163.499999999999</v>
-      </c>
-      <c r="D3" t="n">
-        <v>49.49999999999994</v>
-      </c>
-      <c r="E3" t="n">
-        <v>241.9999999999997</v>
+      <c r="B3" s="3">
+        <v>1433541.3485999971</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1163.4999999999991</v>
+      </c>
+      <c r="D3" s="2">
+        <v>49.499999999999943</v>
+      </c>
+      <c r="E3" s="2">
+        <v>241.99999999999969</v>
+      </c>
+      <c r="F3" s="4">
+        <f t="shared" ref="F3:G5" si="0">D3/C3</f>
+        <v>4.2544048130640291E-2</v>
+      </c>
+      <c r="G3" s="4">
+        <f t="shared" ref="G3:G5" si="1">E3/C3</f>
+        <v>0.2079931241942414</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
         <v>2</v>
       </c>
-      <c r="B4" t="n">
-        <v>2814023.584799996</v>
-      </c>
-      <c r="C4" t="n">
+      <c r="B4" s="3">
+        <v>2814023.5847999961</v>
+      </c>
+      <c r="C4" s="2">
         <v>2743.5</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="2">
         <v>127.5</v>
       </c>
-      <c r="E4" t="n">
-        <v>533.4999999999995</v>
+      <c r="E4" s="2">
+        <v>533.49999999999955</v>
+      </c>
+      <c r="F4" s="4">
+        <f t="shared" si="0"/>
+        <v>4.6473482777474026E-2</v>
+      </c>
+      <c r="G4" s="4">
+        <f t="shared" si="1"/>
+        <v>0.19445963185711665</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
         <v>3</v>
       </c>
-      <c r="B5" t="n">
-        <v>860049.5651999959</v>
-      </c>
-      <c r="C5" t="n">
-        <v>460.9999999999995</v>
-      </c>
-      <c r="D5" t="n">
-        <v>18.99999999999997</v>
-      </c>
-      <c r="E5" t="n">
-        <v>98.9999999999999</v>
+      <c r="B5" s="3">
+        <v>860049.56519999588</v>
+      </c>
+      <c r="C5" s="2">
+        <v>460.99999999999949</v>
+      </c>
+      <c r="D5" s="2">
+        <v>18.999999999999972</v>
+      </c>
+      <c r="E5" s="2">
+        <v>98.999999999999901</v>
+      </c>
+      <c r="F5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.1214750542299332E-2</v>
+      </c>
+      <c r="G5" s="4">
+        <f t="shared" si="1"/>
+        <v>0.21475054229934926</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:B5">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C5">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D5">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E5">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F5">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G5">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>